--- a/grupos/3AEV - Estadisticos 20241.xlsx
+++ b/grupos/3AEV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="95">
   <si>
     <t>Materia</t>
   </si>
@@ -170,10 +170,16 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
+    <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
     <t>Hernández López Elizabeth</t>
@@ -182,12 +188,6 @@
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -203,73 +203,100 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>LARA</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>AUTRAN</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>KEVYN DANIEL</t>
   </si>
   <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>ARMANDO GABRIEL</t>
+  </si>
+  <si>
+    <t>JUAN RAMON</t>
+  </si>
+  <si>
+    <t>TRISTAN YABAL</t>
+  </si>
+  <si>
+    <t>ANGEL CHARBEL</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JOSE EMILIANO</t>
+  </si>
+  <si>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JUAN RAMON</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>AXEL AARON</t>
   </si>
   <si>
     <t>ANTHONY</t>
@@ -821,28 +848,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -878,16 +905,16 @@
         <v>7</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG4">
         <v>-1</v>
@@ -904,10 +931,10 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -919,7 +946,7 @@
         <v>8</v>
       </c>
       <c r="AE5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -951,28 +978,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -999,10 +1026,10 @@
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>7</v>
@@ -1052,28 +1079,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1100,7 +1127,7 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>5</v>
@@ -1109,7 +1136,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD7">
         <v>6</v>
@@ -1153,28 +1180,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1204,22 +1231,22 @@
         <v>9</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD8">
         <v>8</v>
       </c>
       <c r="AE8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG8">
         <v>-1</v>
@@ -1254,28 +1281,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1302,25 +1329,25 @@
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB9">
         <v>6</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG9">
         <v>-1</v>
@@ -1355,28 +1382,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1403,16 +1430,16 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD10">
         <v>5</v>
@@ -1456,28 +1483,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1504,7 +1531,7 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <v>5</v>
@@ -1557,28 +1584,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1605,10 +1632,10 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>6</v>
@@ -1620,10 +1647,10 @@
         <v>6</v>
       </c>
       <c r="AE12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG12">
         <v>-1</v>
@@ -1658,28 +1685,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1706,7 +1733,7 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13">
         <v>5</v>
@@ -1715,7 +1742,7 @@
         <v>6</v>
       </c>
       <c r="AC13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD13">
         <v>5</v>
@@ -1759,28 +1786,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1807,22 +1834,22 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>6</v>
       </c>
       <c r="AC14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD14">
         <v>6</v>
       </c>
       <c r="AE14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF14">
         <v>5</v>
@@ -1860,28 +1887,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1908,7 +1935,7 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>6</v>
@@ -1917,16 +1944,16 @@
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD15">
         <v>6</v>
       </c>
       <c r="AE15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG15">
         <v>-1</v>
@@ -1961,28 +1988,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2012,19 +2039,19 @@
         <v>9</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD16">
         <v>7</v>
       </c>
       <c r="AE16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF16">
         <v>6</v>
@@ -2062,28 +2089,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2113,19 +2140,19 @@
         <v>8</v>
       </c>
       <c r="AA17">
+        <v>10</v>
+      </c>
+      <c r="AB17">
+        <v>8</v>
+      </c>
+      <c r="AC17">
         <v>9</v>
       </c>
-      <c r="AB17">
-        <v>7</v>
-      </c>
-      <c r="AC17">
-        <v>8</v>
-      </c>
       <c r="AD17">
         <v>8</v>
       </c>
       <c r="AE17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF17">
         <v>5</v>
@@ -2163,28 +2190,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2211,7 +2238,7 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>6</v>
@@ -2220,7 +2247,7 @@
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD18">
         <v>5</v>
@@ -2264,28 +2291,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2312,19 +2339,19 @@
         <v>-1</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>5</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE19">
         <v>7</v>
@@ -2365,28 +2392,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2413,16 +2440,16 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB20">
         <v>6</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD20">
         <v>6</v>
@@ -2466,28 +2493,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2514,7 +2541,7 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>5</v>
@@ -2523,7 +2550,7 @@
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD21">
         <v>5</v>
@@ -2567,28 +2594,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2615,7 +2642,7 @@
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>7</v>
@@ -2624,13 +2651,13 @@
         <v>6</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF22">
         <v>7</v>
@@ -2668,28 +2695,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2769,28 +2796,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2817,7 +2844,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -2829,10 +2856,10 @@
         <v>8</v>
       </c>
       <c r="AD24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF24">
         <v>6</v>
@@ -2870,28 +2897,28 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2918,22 +2945,22 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA25">
         <v>7</v>
       </c>
       <c r="AB25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC25">
         <v>5</v>
       </c>
       <c r="AD25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF25">
         <v>7</v>
@@ -3108,22 +3135,22 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="N4">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3132,22 +3159,22 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4">
         <v>100</v>
       </c>
       <c r="U4">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="V4">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="W4">
         <v>100</v>
       </c>
       <c r="X4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -3208,7 +3235,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3217,13 +3244,13 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3232,7 +3259,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T6">
         <v>100</v>
@@ -3241,13 +3268,13 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="W6">
         <v>100</v>
       </c>
       <c r="X6">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y6">
         <v>100</v>
@@ -3285,22 +3312,22 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="L7">
-        <v>62.5</v>
+        <v>81.3</v>
       </c>
       <c r="M7">
-        <v>93.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="P7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3309,22 +3336,22 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T7">
-        <v>62.5</v>
+        <v>81.3</v>
       </c>
       <c r="U7">
-        <v>93.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="V7">
         <v>100</v>
       </c>
       <c r="W7">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="X7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y7">
         <v>100</v>
@@ -3362,22 +3389,22 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="N8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3386,22 +3413,22 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="T8">
         <v>100</v>
       </c>
       <c r="U8">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="V8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="W8">
         <v>100</v>
       </c>
       <c r="X8">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y8">
         <v>100</v>
@@ -3439,19 +3466,19 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>75</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L9">
         <v>100</v>
       </c>
       <c r="M9">
-        <v>81.3</v>
+        <v>90.3</v>
       </c>
       <c r="N9">
         <v>84</v>
       </c>
       <c r="O9">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3463,19 +3490,19 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>75</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="T9">
         <v>100</v>
       </c>
       <c r="U9">
-        <v>81.3</v>
+        <v>90.3</v>
       </c>
       <c r="V9">
         <v>84</v>
       </c>
       <c r="W9">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="X9">
         <v>100</v>
@@ -3516,10 +3543,10 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L10">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -3528,10 +3555,10 @@
         <v>84</v>
       </c>
       <c r="O10">
-        <v>91.7</v>
+        <v>96.2</v>
       </c>
       <c r="P10">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3540,10 +3567,10 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="T10">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -3552,10 +3579,10 @@
         <v>84</v>
       </c>
       <c r="W10">
-        <v>91.7</v>
+        <v>96.2</v>
       </c>
       <c r="X10">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -3593,22 +3620,22 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>75</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N11">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O11">
-        <v>91.7</v>
+        <v>96.2</v>
       </c>
       <c r="P11">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -3617,22 +3644,22 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T11">
         <v>100</v>
       </c>
       <c r="U11">
-        <v>75</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="V11">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="W11">
-        <v>91.7</v>
+        <v>96.2</v>
       </c>
       <c r="X11">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y11">
         <v>100</v>
@@ -3676,7 +3703,7 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>87.5</v>
+        <v>93.5</v>
       </c>
       <c r="N12">
         <v>96</v>
@@ -3700,7 +3727,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>87.5</v>
+        <v>93.5</v>
       </c>
       <c r="V12">
         <v>96</v>
@@ -3747,7 +3774,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>85</v>
+        <v>87.2</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -3756,13 +3783,13 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O13">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="P13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -3771,7 +3798,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>85</v>
+        <v>87.2</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -3780,13 +3807,13 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="W13">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="X13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -3824,22 +3851,22 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L14">
         <v>100</v>
       </c>
       <c r="M14">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="N14">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O14">
         <v>100</v>
       </c>
       <c r="P14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3848,22 +3875,22 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="T14">
         <v>100</v>
       </c>
       <c r="U14">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="V14">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="W14">
         <v>100</v>
       </c>
       <c r="X14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y14">
         <v>100</v>
@@ -3901,22 +3928,22 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>75</v>
+        <v>87.2</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="N15">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="O15">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3925,22 +3952,22 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>75</v>
+        <v>87.2</v>
       </c>
       <c r="T15">
         <v>100</v>
       </c>
       <c r="U15">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="V15">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="W15">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="X15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y15">
         <v>100</v>
@@ -3978,17 +4005,17 @@
         <v>100</v>
       </c>
       <c r="K16">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="L16">
+        <v>100</v>
+      </c>
+      <c r="M16">
+        <v>93.5</v>
+      </c>
+      <c r="N16">
         <v>90</v>
       </c>
-      <c r="L16">
-        <v>100</v>
-      </c>
-      <c r="M16">
-        <v>100</v>
-      </c>
-      <c r="N16">
-        <v>84</v>
-      </c>
       <c r="O16">
         <v>100</v>
       </c>
@@ -4002,16 +4029,16 @@
         <v>100</v>
       </c>
       <c r="S16">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="T16">
+        <v>100</v>
+      </c>
+      <c r="U16">
+        <v>93.5</v>
+      </c>
+      <c r="V16">
         <v>90</v>
-      </c>
-      <c r="T16">
-        <v>100</v>
-      </c>
-      <c r="U16">
-        <v>100</v>
-      </c>
-      <c r="V16">
-        <v>84</v>
       </c>
       <c r="W16">
         <v>100</v>
@@ -4055,22 +4082,22 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
-        <v>87.5</v>
+        <v>93.5</v>
       </c>
       <c r="N17">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -4079,22 +4106,22 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T17">
         <v>100</v>
       </c>
       <c r="U17">
-        <v>87.5</v>
+        <v>93.5</v>
       </c>
       <c r="V17">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="W17">
         <v>100</v>
       </c>
       <c r="X17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y17">
         <v>100</v>
@@ -4132,22 +4159,22 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>90</v>
+        <v>46.2</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="N18">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4156,22 +4183,22 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>90</v>
+        <v>46.2</v>
       </c>
       <c r="T18">
         <v>100</v>
       </c>
       <c r="U18">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="V18">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="W18">
         <v>100</v>
       </c>
       <c r="X18">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y18">
         <v>100</v>
@@ -4209,19 +4236,19 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="N19">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O19">
-        <v>91.7</v>
+        <v>96.2</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -4233,19 +4260,19 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="T19">
         <v>100</v>
       </c>
       <c r="U19">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="V19">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="W19">
-        <v>91.7</v>
+        <v>96.2</v>
       </c>
       <c r="X19">
         <v>100</v>
@@ -4286,22 +4313,22 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L20">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M20">
-        <v>93.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N20">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="O20">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="P20">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4310,22 +4337,22 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="T20">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U20">
-        <v>93.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="V20">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="W20">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="X20">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -4363,22 +4390,22 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="L21">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M21">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="N21">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="O21">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4387,22 +4414,22 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="T21">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U21">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="V21">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="W21">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y21">
         <v>100</v>
@@ -4440,7 +4467,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -4449,7 +4476,7 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -4464,7 +4491,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="T22">
         <v>100</v>
@@ -4473,7 +4500,7 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="W22">
         <v>100</v>
@@ -4517,22 +4544,22 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>50</v>
+        <v>25.6</v>
       </c>
       <c r="L23">
-        <v>31.3</v>
+        <v>15.6</v>
       </c>
       <c r="M23">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="N23">
+        <v>48</v>
+      </c>
+      <c r="O23">
         <v>75</v>
       </c>
-      <c r="N23">
-        <v>88</v>
-      </c>
-      <c r="O23">
-        <v>73.3</v>
-      </c>
       <c r="P23">
-        <v>95</v>
+        <v>72.5</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -4541,22 +4568,22 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>50</v>
+        <v>25.6</v>
       </c>
       <c r="T23">
-        <v>31.3</v>
+        <v>15.6</v>
       </c>
       <c r="U23">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="V23">
+        <v>48</v>
+      </c>
+      <c r="W23">
         <v>75</v>
       </c>
-      <c r="V23">
-        <v>88</v>
-      </c>
-      <c r="W23">
-        <v>73.3</v>
-      </c>
       <c r="X23">
-        <v>95</v>
+        <v>72.5</v>
       </c>
       <c r="Y23">
         <v>100</v>
@@ -4594,16 +4621,16 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>95</v>
+        <v>89.7</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24">
-        <v>93.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="N24">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -4618,16 +4645,16 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>95</v>
+        <v>89.7</v>
       </c>
       <c r="T24">
         <v>100</v>
       </c>
       <c r="U24">
-        <v>93.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="V24">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="W24">
         <v>100</v>
@@ -4671,16 +4698,16 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>90</v>
+        <v>92.3</v>
       </c>
       <c r="L25">
-        <v>31.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M25">
-        <v>75</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N25">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -4695,16 +4722,16 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>90</v>
+        <v>92.3</v>
       </c>
       <c r="T25">
-        <v>31.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="U25">
-        <v>75</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="V25">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="W25">
         <v>100</v>
@@ -4820,7 +4847,7 @@
         <v>52.4</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4831,28 +4858,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
       </c>
       <c r="C4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2">
-        <v>54.5</v>
+        <v>61.9</v>
       </c>
       <c r="G4" s="2">
-        <v>45.5</v>
+        <v>38.1</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4863,28 +4890,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>57.1</v>
+        <v>68.2</v>
       </c>
       <c r="G5" s="2">
-        <v>42.9</v>
+        <v>31.8</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4895,25 +4922,25 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>61.9</v>
+        <v>68.2</v>
       </c>
       <c r="G6" s="2">
-        <v>38.1</v>
+        <v>31.8</v>
       </c>
       <c r="H6">
         <v>6.5</v>
@@ -4927,7 +4954,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -4936,19 +4963,19 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4959,7 +4986,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>54</v>
@@ -4968,19 +4995,19 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>71.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G8" s="2">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
       <c r="H8">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4991,28 +5018,28 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>55</v>
       </c>
       <c r="C9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>72.7</v>
+        <v>95.2</v>
       </c>
       <c r="G9" s="2">
-        <v>27.3</v>
+        <v>4.8</v>
       </c>
       <c r="H9">
-        <v>6.3</v>
+        <v>7.7</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -5062,7 +5089,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5100,16 +5127,16 @@
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5123,10 +5150,10 @@
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -5140,22 +5167,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920199</v>
+        <v>23330051920329</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5163,16 +5190,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920199</v>
+        <v>23330051920329</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -5186,22 +5213,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920201</v>
+        <v>23330051920324</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5209,16 +5236,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920201</v>
+        <v>23330051920324</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -5232,22 +5259,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920211</v>
+        <v>23330051920201</v>
       </c>
       <c r="B8" t="s">
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5255,16 +5282,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920211</v>
+        <v>23330051920201</v>
       </c>
       <c r="B9" t="s">
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -5278,39 +5305,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920179</v>
+        <v>22330051920196</v>
       </c>
       <c r="B10" t="s">
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920180</v>
+        <v>22330051920196</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -5324,39 +5351,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920190</v>
+        <v>22330051920050</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920206</v>
+        <v>22330051920050</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -5370,16 +5397,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920186</v>
+        <v>23330051920179</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
@@ -5388,6 +5415,121 @@
         <v>48</v>
       </c>
       <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920180</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920190</v>
+      </c>
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920199</v>
+      </c>
+      <c r="B17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920206</v>
+      </c>
+      <c r="B18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920186</v>
+      </c>
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3AEV - Estadisticos 20241.xlsx
+++ b/grupos/3AEV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -200,6 +200,18 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -224,6 +236,15 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -243,6 +264,18 @@
   </si>
   <si>
     <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
   </si>
   <si>
     <t>LUIS FABIAN</t>
@@ -4575,7 +4608,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4607,22 +4640,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920203</v>
+        <v>23330051920183</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4630,22 +4663,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920203</v>
+        <v>23330051920183</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4653,22 +4686,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920211</v>
+        <v>23330051920183</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4676,22 +4709,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920211</v>
+        <v>23330051920183</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4699,22 +4732,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920192</v>
+        <v>23330051920189</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4722,22 +4755,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920329</v>
+        <v>23330051920189</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4745,22 +4778,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920324</v>
+        <v>23330051920189</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4768,16 +4801,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920201</v>
+        <v>23330051920189</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -4791,22 +4824,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920196</v>
+        <v>23330051920195</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4814,24 +4847,392 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920050</v>
+        <v>23330051920195</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
         <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920195</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920195</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920202</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920202</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920202</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920202</v>
+      </c>
+      <c r="B17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920203</v>
+      </c>
+      <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920203</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920211</v>
+      </c>
+      <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920211</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920192</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920329</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920324</v>
+      </c>
+      <c r="B24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920201</v>
+      </c>
+      <c r="B25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920196</v>
+      </c>
+      <c r="B26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>22330051920050</v>
+      </c>
+      <c r="B27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
         <v>53</v>
       </c>
-      <c r="G11">
+      <c r="G27">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEV - Estadisticos 20241.xlsx
+++ b/grupos/3AEV - Estadisticos 20241.xlsx
@@ -2834,7 +2834,7 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>93.8</v>
+        <v>83.3</v>
       </c>
       <c r="F4">
         <v>88</v>
@@ -2855,7 +2855,7 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M4">
         <v>86</v>
@@ -2876,7 +2876,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T4">
         <v>86</v>
@@ -2925,7 +2925,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F6">
         <v>96</v>
@@ -2946,7 +2946,7 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M6">
         <v>98</v>
@@ -2967,7 +2967,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="T6">
         <v>98</v>
@@ -2993,7 +2993,7 @@
         <v>62.5</v>
       </c>
       <c r="E7">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -3014,7 +3014,7 @@
         <v>81.3</v>
       </c>
       <c r="L7">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -3035,7 +3035,7 @@
         <v>81.3</v>
       </c>
       <c r="S7">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T7">
         <v>100</v>
@@ -3061,7 +3061,7 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>93.8</v>
+        <v>83.3</v>
       </c>
       <c r="F8">
         <v>96</v>
@@ -3082,7 +3082,7 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M8">
         <v>98</v>
@@ -3103,7 +3103,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T8">
         <v>98</v>
@@ -3129,7 +3129,7 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>81.3</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>84</v>
@@ -3150,7 +3150,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>90.3</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>84</v>
@@ -3171,7 +3171,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>90.3</v>
+        <v>100</v>
       </c>
       <c r="T9">
         <v>84</v>
@@ -3197,7 +3197,7 @@
         <v>81.3</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F10">
         <v>84</v>
@@ -3218,7 +3218,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M10">
         <v>84</v>
@@ -3239,7 +3239,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="T10">
         <v>84</v>
@@ -3265,7 +3265,7 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>80</v>
@@ -3286,7 +3286,7 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>82</v>
@@ -3307,7 +3307,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T11">
         <v>82</v>
@@ -3333,7 +3333,7 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>87.5</v>
+        <v>77.8</v>
       </c>
       <c r="F12">
         <v>96</v>
@@ -3354,7 +3354,7 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>93.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="M12">
         <v>96</v>
@@ -3375,7 +3375,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>93.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="T12">
         <v>96</v>
@@ -3401,7 +3401,7 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F13">
         <v>80</v>
@@ -3422,7 +3422,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M13">
         <v>82</v>
@@ -3443,7 +3443,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="T13">
         <v>82</v>
@@ -3469,7 +3469,7 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>93.8</v>
+        <v>83.3</v>
       </c>
       <c r="F14">
         <v>64</v>
@@ -3490,7 +3490,7 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M14">
         <v>72</v>
@@ -3511,7 +3511,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T14">
         <v>72</v>
@@ -3537,7 +3537,7 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>93.8</v>
+        <v>83.3</v>
       </c>
       <c r="F15">
         <v>88</v>
@@ -3558,7 +3558,7 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M15">
         <v>84</v>
@@ -3579,7 +3579,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T15">
         <v>84</v>
@@ -3605,7 +3605,7 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F16">
         <v>84</v>
@@ -3626,7 +3626,7 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>93.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="M16">
         <v>90</v>
@@ -3647,7 +3647,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>93.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="T16">
         <v>90</v>
@@ -3673,7 +3673,7 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>87.5</v>
+        <v>77.8</v>
       </c>
       <c r="F17">
         <v>96</v>
@@ -3694,7 +3694,7 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>93.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="M17">
         <v>98</v>
@@ -3715,7 +3715,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>93.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="T17">
         <v>98</v>
@@ -3741,7 +3741,7 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>93.8</v>
+        <v>83.3</v>
       </c>
       <c r="F18">
         <v>60</v>
@@ -3762,7 +3762,7 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M18">
         <v>70</v>
@@ -3783,7 +3783,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T18">
         <v>70</v>
@@ -3809,7 +3809,7 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>93.8</v>
+        <v>83.3</v>
       </c>
       <c r="F19">
         <v>96</v>
@@ -3830,7 +3830,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M19">
         <v>98</v>
@@ -3851,7 +3851,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T19">
         <v>98</v>
@@ -3877,7 +3877,7 @@
         <v>81.3</v>
       </c>
       <c r="E20">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>72</v>
@@ -3898,7 +3898,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="L20">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="M20">
         <v>80</v>
@@ -3919,7 +3919,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S20">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T20">
         <v>80</v>
@@ -3945,7 +3945,7 @@
         <v>81.3</v>
       </c>
       <c r="E21">
-        <v>93.8</v>
+        <v>83.3</v>
       </c>
       <c r="F21">
         <v>76</v>
@@ -3966,7 +3966,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="L21">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M21">
         <v>82</v>
@@ -3987,7 +3987,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S21">
-        <v>96.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T21">
         <v>82</v>
@@ -4013,7 +4013,7 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F22">
         <v>88</v>
@@ -4034,7 +4034,7 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M22">
         <v>92</v>
@@ -4055,7 +4055,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="T22">
         <v>92</v>
@@ -4081,7 +4081,7 @@
         <v>31.3</v>
       </c>
       <c r="E23">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="F23">
         <v>88</v>
@@ -4102,7 +4102,7 @@
         <v>15.6</v>
       </c>
       <c r="L23">
-        <v>87.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="M23">
         <v>48</v>
@@ -4123,7 +4123,7 @@
         <v>15.6</v>
       </c>
       <c r="S23">
-        <v>87.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="T23">
         <v>48</v>
@@ -4149,7 +4149,7 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>93.8</v>
+        <v>83.3</v>
       </c>
       <c r="F24">
         <v>84</v>
@@ -4170,7 +4170,7 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>83.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M24">
         <v>78</v>
@@ -4191,7 +4191,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>83.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T24">
         <v>78</v>
@@ -4217,7 +4217,7 @@
         <v>31.3</v>
       </c>
       <c r="E25">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>76</v>
@@ -4238,7 +4238,7 @@
         <v>65.59999999999999</v>
       </c>
       <c r="L25">
-        <v>80.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M25">
         <v>88</v>
@@ -4259,7 +4259,7 @@
         <v>65.59999999999999</v>
       </c>
       <c r="S25">
-        <v>80.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="T25">
         <v>88</v>

--- a/grupos/3AEV - Estadisticos 20241.xlsx
+++ b/grupos/3AEV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -167,18 +167,18 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
     <t>Hernández López Elizabeth</t>
   </si>
   <si>
@@ -200,16 +200,25 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>CHICO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>NARVAEZ</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
   </si>
   <si>
     <t>PEREZ</t>
@@ -218,31 +227,28 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>MIRON</t>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
   </si>
   <si>
     <t>DE JESUS</t>
@@ -251,52 +257,37 @@
     <t>CARRILLO</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
     <t>CAMPOS</t>
   </si>
   <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
     <t>FERNANDO</t>
   </si>
   <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>LAZARO</t>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>JUAN RAMON</t>
   </si>
   <si>
     <t>LUIS FABIAN</t>
   </si>
   <si>
     <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
-    <t>SABDY</t>
-  </si>
-  <si>
-    <t>ARMANDO GABRIEL</t>
-  </si>
-  <si>
-    <t>JUAN RAMON</t>
-  </si>
-  <si>
-    <t>TRISTAN YABAL</t>
   </si>
   <si>
     <t>ANGEL CHARBEL</t>
@@ -850,19 +841,19 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -883,7 +874,7 @@
         <v>7</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -909,7 +900,7 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA5">
         <v>8</v>
@@ -968,19 +959,19 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -989,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1001,7 +992,7 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>6</v>
@@ -1057,19 +1048,19 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>-1</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1078,10 +1069,10 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>8</v>
@@ -1090,7 +1081,7 @@
         <v>6</v>
       </c>
       <c r="AB7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC7">
         <v>5</v>
@@ -1146,19 +1137,19 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>-1</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1235,19 +1226,19 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1324,19 +1315,19 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1348,16 +1339,16 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA10">
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1413,19 +1404,19 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1434,10 +1425,10 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -1502,19 +1493,19 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1523,19 +1514,19 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>6</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>6</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1591,19 +1582,19 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -1612,7 +1603,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1680,19 +1671,19 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1707,7 +1698,7 @@
         <v>6</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>6</v>
@@ -1769,19 +1760,19 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1793,10 +1784,10 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>6</v>
@@ -1858,19 +1849,19 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1947,19 +1938,19 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>-1</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -1968,7 +1959,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2036,19 +2027,19 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>-1</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -2057,7 +2048,7 @@
         <v>8</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2125,19 +2116,19 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>-1</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -2149,10 +2140,10 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA19">
         <v>7</v>
@@ -2214,19 +2205,19 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2235,7 +2226,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2247,7 +2238,7 @@
         <v>6</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>5</v>
@@ -2303,19 +2294,19 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2327,16 +2318,16 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>5</v>
       </c>
       <c r="AB21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2392,19 +2383,19 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2481,19 +2472,19 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2570,19 +2561,19 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2591,7 +2582,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2659,19 +2650,19 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>-1</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2683,16 +2674,16 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>7</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>7</v>
@@ -2870,13 +2861,13 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>94.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="R4">
         <v>100</v>
       </c>
       <c r="S4">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T4">
         <v>86</v>
@@ -2908,7 +2899,7 @@
         <v>84</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -2961,19 +2952,19 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>93.7</v>
       </c>
       <c r="R6">
         <v>100</v>
       </c>
       <c r="S6">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T6">
         <v>98</v>
       </c>
       <c r="U6">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V6">
         <v>97.5</v>
@@ -3029,10 +3020,10 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>94.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="R7">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3041,7 +3032,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V7">
         <v>97.5</v>
@@ -3097,13 +3088,13 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>97.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T8">
         <v>98</v>
@@ -3165,7 +3156,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>84.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -3177,7 +3168,7 @@
         <v>84</v>
       </c>
       <c r="U9">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -3233,19 +3224,19 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>97.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="R10">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="S10">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T10">
         <v>84</v>
       </c>
       <c r="U10">
-        <v>96.2</v>
+        <v>95.3</v>
       </c>
       <c r="V10">
         <v>97.5</v>
@@ -3301,7 +3292,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -3313,7 +3304,7 @@
         <v>82</v>
       </c>
       <c r="U11">
-        <v>96.2</v>
+        <v>95.3</v>
       </c>
       <c r="V11">
         <v>97.5</v>
@@ -3375,7 +3366,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="T12">
         <v>96</v>
@@ -3437,19 +3428,19 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>87.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T13">
         <v>82</v>
       </c>
       <c r="U13">
-        <v>95.5</v>
+        <v>94.3</v>
       </c>
       <c r="V13">
         <v>97.5</v>
@@ -3505,19 +3496,19 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>97.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T14">
         <v>72</v>
       </c>
       <c r="U14">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V14">
         <v>97.5</v>
@@ -3573,19 +3564,19 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>87.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R15">
         <v>100</v>
       </c>
       <c r="S15">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T15">
         <v>84</v>
       </c>
       <c r="U15">
-        <v>93.2</v>
+        <v>94.3</v>
       </c>
       <c r="V15">
         <v>97.5</v>
@@ -3641,13 +3632,13 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>94.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="R16">
         <v>100</v>
       </c>
       <c r="S16">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="T16">
         <v>90</v>
@@ -3709,19 +3700,19 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R17">
         <v>100</v>
       </c>
       <c r="S17">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="T17">
         <v>98</v>
       </c>
       <c r="U17">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V17">
         <v>97.5</v>
@@ -3756,7 +3747,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>46.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -3777,19 +3768,19 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>46.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="S18">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T18">
         <v>70</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="V18">
         <v>97.5</v>
@@ -3845,19 +3836,19 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R19">
         <v>100</v>
       </c>
       <c r="S19">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T19">
         <v>98</v>
       </c>
       <c r="U19">
-        <v>96.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -3913,10 +3904,10 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R20">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -3925,7 +3916,7 @@
         <v>80</v>
       </c>
       <c r="U20">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V20">
         <v>97.5</v>
@@ -3981,19 +3972,19 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>25.6</v>
+        <v>52.4</v>
       </c>
       <c r="R21">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="S21">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T21">
         <v>82</v>
       </c>
       <c r="U21">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V21">
         <v>97.5</v>
@@ -4049,13 +4040,13 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R22">
         <v>100</v>
       </c>
       <c r="S22">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T22">
         <v>92</v>
@@ -4117,19 +4108,19 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>25.6</v>
+        <v>15.9</v>
       </c>
       <c r="R23">
-        <v>15.6</v>
+        <v>10.4</v>
       </c>
       <c r="S23">
-        <v>81.8</v>
+        <v>87.5</v>
       </c>
       <c r="T23">
         <v>48</v>
       </c>
       <c r="U23">
-        <v>75</v>
+        <v>80.2</v>
       </c>
       <c r="V23">
         <v>72.5</v>
@@ -4185,13 +4176,13 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>89.7</v>
+        <v>93.7</v>
       </c>
       <c r="R24">
         <v>100</v>
       </c>
       <c r="S24">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T24">
         <v>78</v>
@@ -4253,13 +4244,13 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>92.3</v>
+        <v>95.2</v>
       </c>
       <c r="R25">
-        <v>65.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="S25">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T25">
         <v>88</v>
@@ -4357,28 +4348,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
       </c>
       <c r="C3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>61.9</v>
+        <v>68.2</v>
       </c>
       <c r="G3" s="2">
-        <v>38.1</v>
+        <v>31.8</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4389,28 +4380,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
       </c>
       <c r="C4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>68.2</v>
+        <v>85.7</v>
       </c>
       <c r="G4" s="2">
-        <v>31.8</v>
+        <v>14.3</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4421,28 +4412,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
       </c>
       <c r="C5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>68.2</v>
+        <v>85.7</v>
       </c>
       <c r="G5" s="2">
-        <v>31.8</v>
+        <v>14.3</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4453,28 +4444,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>71.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>28.6</v>
+        <v>13.6</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4494,19 +4485,19 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>85.7</v>
+        <v>90.5</v>
       </c>
       <c r="G7" s="2">
-        <v>14.3</v>
+        <v>9.5</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4608,7 +4599,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4640,22 +4631,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920183</v>
+        <v>22330051920389</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4663,19 +4654,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920183</v>
+        <v>22330051920389</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>49</v>
@@ -4686,22 +4677,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920183</v>
+        <v>22330051920389</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4709,22 +4700,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920183</v>
+        <v>23330051920195</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4732,22 +4723,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920189</v>
+        <v>23330051920195</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4755,22 +4746,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920189</v>
+        <v>23330051920195</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4778,22 +4769,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920189</v>
+        <v>23330051920332</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4801,22 +4792,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920189</v>
+        <v>23330051920332</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4824,22 +4815,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920195</v>
+        <v>23330051920332</v>
       </c>
       <c r="B10" t="s">
         <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4847,22 +4838,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920195</v>
+        <v>23330051920189</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4870,22 +4861,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920195</v>
+        <v>23330051920189</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -4893,10 +4884,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920195</v>
+        <v>23330051920183</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
         <v>74</v>
@@ -4916,22 +4907,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920202</v>
+        <v>23330051920192</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
         <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -4939,22 +4930,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920202</v>
+        <v>23330051920329</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -4962,22 +4953,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920202</v>
+        <v>23330051920201</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -4985,16 +4976,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920202</v>
+        <v>23330051920203</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
@@ -5008,22 +4999,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920203</v>
+        <v>23330051920211</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -5031,208 +5022,24 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920203</v>
+        <v>22330051920050</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920211</v>
-      </c>
-      <c r="B20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920211</v>
-      </c>
-      <c r="B21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>50</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920192</v>
-      </c>
-      <c r="B22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" t="s">
-        <v>48</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920329</v>
-      </c>
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920324</v>
-      </c>
-      <c r="B24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>49</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920201</v>
-      </c>
-      <c r="B25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" t="s">
-        <v>48</v>
-      </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920196</v>
-      </c>
-      <c r="B26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>49</v>
-      </c>
-      <c r="G26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920050</v>
-      </c>
-      <c r="B27" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEV - Estadisticos 20241.xlsx
+++ b/grupos/3AEV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -212,15 +212,9 @@
     <t>CHICO</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -239,15 +233,12 @@
     <t>SUAREZ</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>GUEVARA</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>CIRUELO</t>
   </si>
   <si>
@@ -269,19 +260,13 @@
     <t>SERGIO JOSUE</t>
   </si>
   <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
     <t>NATANAHEL</t>
   </si>
   <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
     <t>SABDY</t>
-  </si>
-  <si>
-    <t>JUAN RAMON</t>
   </si>
   <si>
     <t>LUIS FABIAN</t>
@@ -856,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -877,7 +862,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -974,7 +959,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1063,7 +1048,7 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1152,7 +1137,7 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1173,7 +1158,7 @@
         <v>8</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1241,7 +1226,7 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1330,7 +1315,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1351,7 +1336,7 @@
         <v>6</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1419,7 +1404,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1508,7 +1493,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1529,7 +1514,7 @@
         <v>7</v>
       </c>
       <c r="AC12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1597,7 +1582,7 @@
         <v>6</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1686,7 +1671,7 @@
         <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1775,7 +1760,7 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1796,7 +1781,7 @@
         <v>6</v>
       </c>
       <c r="AC15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1864,7 +1849,7 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -1953,7 +1938,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -1974,7 +1959,7 @@
         <v>7</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2042,7 +2027,7 @@
         <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2131,7 +2116,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2152,7 +2137,7 @@
         <v>7</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2220,7 +2205,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2309,7 +2294,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2398,7 +2383,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2487,7 +2472,7 @@
         <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2576,7 +2561,7 @@
         <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2665,7 +2650,7 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2686,7 +2671,7 @@
         <v>8</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2876,7 +2861,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -2967,7 +2952,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="V6">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3035,7 +3020,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V7">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3103,7 +3088,7 @@
         <v>100</v>
       </c>
       <c r="V8">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3239,7 +3224,7 @@
         <v>95.3</v>
       </c>
       <c r="V10">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3307,7 +3292,7 @@
         <v>95.3</v>
       </c>
       <c r="V11">
-        <v>97.5</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3443,7 +3428,7 @@
         <v>94.3</v>
       </c>
       <c r="V13">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3511,7 +3496,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="V14">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3579,7 +3564,7 @@
         <v>94.3</v>
       </c>
       <c r="V15">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3715,7 +3700,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="V17">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3783,7 +3768,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="V18">
-        <v>97.5</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -3919,7 +3904,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V20">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -3987,7 +3972,7 @@
         <v>95.8</v>
       </c>
       <c r="V21">
-        <v>97.5</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4123,7 +4108,7 @@
         <v>80.2</v>
       </c>
       <c r="V23">
-        <v>72.5</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4325,19 +4310,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>47.6</v>
+        <v>61.9</v>
       </c>
       <c r="G2" s="2">
-        <v>52.4</v>
+        <v>38.1</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4599,7 +4584,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4637,10 +4622,10 @@
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4660,10 +4645,10 @@
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4683,10 +4668,10 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -4706,10 +4691,10 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -4729,10 +4714,10 @@
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -4752,10 +4737,10 @@
         <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -4775,10 +4760,10 @@
         <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4798,10 +4783,10 @@
         <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -4821,10 +4806,10 @@
         <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -4838,22 +4823,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920189</v>
+        <v>23330051920183</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4867,16 +4852,16 @@
         <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -4884,16 +4869,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920183</v>
+        <v>23330051920329</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -4907,16 +4892,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920192</v>
+        <v>23330051920203</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
@@ -4930,22 +4915,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920329</v>
+        <v>23330051920211</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -4953,93 +4938,24 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920201</v>
+        <v>22330051920050</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920203</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920211</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" t="s">
-        <v>89</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920050</v>
-      </c>
-      <c r="B19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEV - Estadisticos 20241.xlsx
+++ b/grupos/3AEV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="81">
   <si>
     <t>Materia</t>
   </si>
@@ -167,21 +167,21 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Hernández López Elizabeth</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Hernández López Elizabeth</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -218,9 +218,6 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
@@ -236,18 +233,12 @@
     <t>RIVERA</t>
   </si>
   <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
     <t>CIRUELO</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
     <t>CAMPOS</t>
   </si>
   <si>
@@ -263,16 +254,10 @@
     <t>FERNANDO</t>
   </si>
   <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
     <t>SABDY</t>
   </si>
   <si>
     <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
   </si>
   <si>
     <t>ANGEL CHARBEL</t>
@@ -823,7 +808,7 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>9</v>
@@ -835,7 +820,7 @@
         <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -882,7 +867,7 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -941,7 +926,7 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>5</v>
@@ -953,7 +938,7 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>7</v>
@@ -1030,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1042,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1119,7 +1104,7 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>9</v>
@@ -1131,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1152,7 +1137,7 @@
         <v>9</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -1208,7 +1193,7 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>7</v>
@@ -1220,7 +1205,7 @@
         <v>8</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1297,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1309,7 +1294,7 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -1330,7 +1315,7 @@
         <v>9</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB10">
         <v>6</v>
@@ -1386,7 +1371,7 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1398,7 +1383,7 @@
         <v>5</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1419,7 +1404,7 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB11">
         <v>7</v>
@@ -1475,7 +1460,7 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>9</v>
@@ -1487,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1508,7 +1493,7 @@
         <v>9</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>7</v>
@@ -1564,7 +1549,7 @@
         <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
         <v>9</v>
@@ -1576,7 +1561,7 @@
         <v>6</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>6</v>
@@ -1597,7 +1582,7 @@
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <v>5</v>
@@ -1653,7 +1638,7 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>7</v>
@@ -1665,7 +1650,7 @@
         <v>6</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -1742,7 +1727,7 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>6</v>
@@ -1754,7 +1739,7 @@
         <v>9</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -1763,7 +1748,7 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1831,7 +1816,7 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -1843,7 +1828,7 @@
         <v>8</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1920,7 +1905,7 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>9</v>
@@ -1932,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -2009,7 +1994,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -2021,7 +2006,7 @@
         <v>6</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2030,7 +2015,7 @@
         <v>5</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -2098,7 +2083,7 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>7</v>
@@ -2110,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>8</v>
@@ -2131,7 +2116,7 @@
         <v>9</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -2187,7 +2172,7 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -2199,7 +2184,7 @@
         <v>7</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2276,7 +2261,7 @@
         <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>5</v>
@@ -2288,7 +2273,7 @@
         <v>8</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2297,7 +2282,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2309,7 +2294,7 @@
         <v>7</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB21">
         <v>6</v>
@@ -2365,7 +2350,7 @@
         <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
         <v>7</v>
@@ -2377,7 +2362,7 @@
         <v>8</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2386,7 +2371,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2398,7 +2383,7 @@
         <v>9</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB22">
         <v>8</v>
@@ -2454,7 +2439,7 @@
         <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -2466,7 +2451,7 @@
         <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>5</v>
@@ -2543,7 +2528,7 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>9</v>
@@ -2555,7 +2540,7 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>8</v>
@@ -2564,7 +2549,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2576,7 +2561,7 @@
         <v>8</v>
       </c>
       <c r="AA24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB24">
         <v>7</v>
@@ -2632,7 +2617,7 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>8</v>
@@ -2644,7 +2629,7 @@
         <v>7</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
         <v>8</v>
@@ -2653,7 +2638,7 @@
         <v>5</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2855,7 +2840,7 @@
         <v>93.8</v>
       </c>
       <c r="T4">
-        <v>86</v>
+        <v>91.3</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -2881,7 +2866,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="U5">
         <v>98.40000000000001</v>
@@ -2946,7 +2931,7 @@
         <v>95.8</v>
       </c>
       <c r="T6">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="U6">
         <v>98.40000000000001</v>
@@ -3082,7 +3067,7 @@
         <v>93.8</v>
       </c>
       <c r="T8">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -3150,7 +3135,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U9">
         <v>93.8</v>
@@ -3218,7 +3203,7 @@
         <v>95.8</v>
       </c>
       <c r="T10">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="U10">
         <v>95.3</v>
@@ -3286,7 +3271,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>82</v>
+        <v>86.3</v>
       </c>
       <c r="U11">
         <v>95.3</v>
@@ -3354,7 +3339,7 @@
         <v>91.7</v>
       </c>
       <c r="T12">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -3422,7 +3407,7 @@
         <v>95.8</v>
       </c>
       <c r="T13">
-        <v>82</v>
+        <v>83.8</v>
       </c>
       <c r="U13">
         <v>94.3</v>
@@ -3490,7 +3475,7 @@
         <v>93.8</v>
       </c>
       <c r="T14">
-        <v>72</v>
+        <v>82.5</v>
       </c>
       <c r="U14">
         <v>98.40000000000001</v>
@@ -3558,7 +3543,7 @@
         <v>93.8</v>
       </c>
       <c r="T15">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="U15">
         <v>94.3</v>
@@ -3626,7 +3611,7 @@
         <v>91.7</v>
       </c>
       <c r="T16">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -3694,7 +3679,7 @@
         <v>91.7</v>
       </c>
       <c r="T17">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="U17">
         <v>98.40000000000001</v>
@@ -3750,7 +3735,7 @@
         <v>97.5</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q18">
         <v>92.09999999999999</v>
@@ -3762,7 +3747,7 @@
         <v>93.8</v>
       </c>
       <c r="T18">
-        <v>70</v>
+        <v>62.5</v>
       </c>
       <c r="U18">
         <v>97.40000000000001</v>
@@ -3830,7 +3815,7 @@
         <v>93.8</v>
       </c>
       <c r="T19">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="U19">
         <v>96.40000000000001</v>
@@ -3898,7 +3883,7 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="U20">
         <v>97.90000000000001</v>
@@ -3966,7 +3951,7 @@
         <v>93.8</v>
       </c>
       <c r="T21">
-        <v>82</v>
+        <v>83.8</v>
       </c>
       <c r="U21">
         <v>95.8</v>
@@ -4034,7 +4019,7 @@
         <v>95.8</v>
       </c>
       <c r="T22">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -4090,7 +4075,7 @@
         <v>72.5</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>79.7</v>
       </c>
       <c r="Q23">
         <v>15.9</v>
@@ -4102,7 +4087,7 @@
         <v>87.5</v>
       </c>
       <c r="T23">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="U23">
         <v>80.2</v>
@@ -4170,7 +4155,7 @@
         <v>93.8</v>
       </c>
       <c r="T24">
-        <v>78</v>
+        <v>86.3</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -4238,7 +4223,7 @@
         <v>95.8</v>
       </c>
       <c r="T25">
-        <v>88</v>
+        <v>92.5</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -4333,28 +4318,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>68.2</v>
+        <v>85.7</v>
       </c>
       <c r="G3" s="2">
-        <v>31.8</v>
+        <v>14.3</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4365,7 +4350,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -4386,7 +4371,7 @@
         <v>14.3</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4397,28 +4382,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>85.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4429,28 +4414,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>19</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>86.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="G6" s="2">
-        <v>13.6</v>
+        <v>9.5</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4461,28 +4446,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
       </c>
       <c r="C7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>90.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4514,7 +4499,7 @@
         <v>4.8</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4584,7 +4569,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4622,16 +4607,16 @@
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4645,16 +4630,16 @@
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4662,22 +4647,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920389</v>
+        <v>23330051920195</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
         <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4691,16 +4676,16 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4708,22 +4693,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920195</v>
+        <v>23330051920332</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4731,16 +4716,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920195</v>
+        <v>23330051920332</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -4754,22 +4739,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920332</v>
+        <v>23330051920183</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4777,22 +4762,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920332</v>
+        <v>23330051920329</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4800,13 +4785,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920332</v>
+        <v>23330051920203</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
         <v>79</v>
@@ -4823,139 +4808,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920183</v>
+        <v>22330051920050</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
         <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920189</v>
-      </c>
-      <c r="B12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920329</v>
-      </c>
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920203</v>
-      </c>
-      <c r="B14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920211</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920050</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" t="s">
-        <v>85</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>
